--- a/sektorler/Endüstriyel Makine -Teçhizat Üretim.xlsx
+++ b/sektorler/Endüstriyel Makine -Teçhizat Üretim.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,177 +417,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ana Ortaklığa Ait Özkaynaklar</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ödenmiş Sermaye</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net_borc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>duzeltilmis_fiyat</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Satış Gelirleri</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net Faaliyet Kar/Zararı</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FAVÖK</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ana Ortaklık Payları</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>F/K</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FD/FAVÖK</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FD/NS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>PD/DD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>NFK/PD_%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Sektör</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>F/K (PD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>FD/FAVÖK (PD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FD/NS (PD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>PD/DD (PD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin PD</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin Fiyat</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>iskonto_%</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SANEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>140767560</v>
+        <v>202339880</v>
       </c>
       <c r="C2" t="n">
         <v>18255333</v>
       </c>
       <c r="D2" t="n">
-        <v>-9175022</v>
+        <v>6392454</v>
       </c>
       <c r="E2" t="n">
-        <v>34.72000122070312</v>
+        <v>40.70000076293945</v>
       </c>
       <c r="F2" t="n">
-        <v>633825184.044342</v>
+        <v>742992067.0277138</v>
       </c>
       <c r="G2" t="n">
-        <v>624650162.044342</v>
+        <v>749384521.0277138</v>
       </c>
       <c r="H2" t="n">
-        <v>343473680</v>
+        <v>348688524</v>
       </c>
       <c r="I2" t="n">
-        <v>60088357</v>
+        <v>76000978</v>
       </c>
       <c r="J2" t="n">
-        <v>68916630</v>
+        <v>109725621</v>
       </c>
       <c r="K2" t="n">
-        <v>115142225</v>
+        <v>299895541</v>
       </c>
       <c r="L2" t="n">
-        <v>5.504715442526336</v>
+        <v>2.477502881670767</v>
       </c>
       <c r="M2" t="n">
-        <v>9.063852397372623</v>
+        <v>6.829622053610558</v>
       </c>
       <c r="N2" t="n">
-        <v>1.818625992082834</v>
+        <v>2.149151662438176</v>
       </c>
       <c r="O2" t="n">
-        <v>4.502636715762794</v>
+        <v>3.672000136738807</v>
       </c>
       <c r="P2" t="n">
-        <v>9.480272875335331</v>
+        <v>10.2290429969241</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -608,74 +596,74 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>1500155163.081657</v>
+        <v>4278018435.42782</v>
       </c>
       <c r="T2" t="n">
-        <v>1026094340.860813</v>
+        <v>1806549494.797907</v>
       </c>
       <c r="U2" t="n">
-        <v>292385578.3972694</v>
+        <v>844040382.3322484</v>
       </c>
       <c r="V2" t="n">
-        <v>939545027.4465798</v>
+        <v>2309536104.185992</v>
       </c>
       <c r="W2" t="n">
-        <v>51.46687970285613</v>
+        <v>126.5129540056044</v>
       </c>
       <c r="X2" t="n">
-        <v>-32.53913697282808</v>
+        <v>-67.82938072797154</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>MAKIM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1123240928</v>
+        <v>1236382849</v>
       </c>
       <c r="C3" t="n">
         <v>112000000</v>
       </c>
       <c r="D3" t="n">
-        <v>58309464</v>
+        <v>145470852</v>
       </c>
       <c r="E3" t="n">
-        <v>18.95000076293945</v>
+        <v>17.36000061035156</v>
       </c>
       <c r="F3" t="n">
-        <v>2122400085.449219</v>
+        <v>1944320068.359375</v>
       </c>
       <c r="G3" t="n">
-        <v>2180709549.449219</v>
+        <v>2089790920.359375</v>
       </c>
       <c r="H3" t="n">
-        <v>1397052272</v>
+        <v>1574889416</v>
       </c>
       <c r="I3" t="n">
-        <v>138591197</v>
+        <v>173314488</v>
       </c>
       <c r="J3" t="n">
-        <v>172356541</v>
+        <v>211324815</v>
       </c>
       <c r="K3" t="n">
-        <v>19825755</v>
+        <v>3234081</v>
       </c>
       <c r="L3" t="n">
-        <v>107.0526739309156</v>
+        <v>601.1970845378873</v>
       </c>
       <c r="M3" t="n">
-        <v>12.65231674293823</v>
+        <v>9.888999171059844</v>
       </c>
       <c r="N3" t="n">
-        <v>1.560936260693629</v>
+        <v>1.326944545520633</v>
       </c>
       <c r="O3" t="n">
-        <v>1.889532363487042</v>
+        <v>1.572587382566785</v>
       </c>
       <c r="P3" t="n">
-        <v>6.529927978714076</v>
+        <v>8.913886701084325</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -684,72 +672,72 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>3670546398.750782</v>
+        <v>8106041696.671924</v>
       </c>
       <c r="T3" t="n">
-        <v>4077930159.528625</v>
+        <v>8042877460.215283</v>
       </c>
       <c r="U3" t="n">
-        <v>2333062023.755798</v>
+        <v>5157446236.396872</v>
       </c>
       <c r="V3" t="n">
-        <v>3360512860.678401</v>
+        <v>7102121797.76136</v>
       </c>
       <c r="W3" t="n">
-        <v>30.00457911320001</v>
+        <v>63.41180176572643</v>
       </c>
       <c r="X3" t="n">
-        <v>-36.84297089638988</v>
+        <v>-72.62339166061277</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>IMASM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3050007000</v>
+        <v>3219973000</v>
       </c>
       <c r="C4" t="n">
         <v>925000000</v>
       </c>
       <c r="D4" t="n">
-        <v>384586000</v>
+        <v>578287000</v>
       </c>
       <c r="E4" t="n">
-        <v>3.960000038146973</v>
+        <v>3.5</v>
       </c>
       <c r="F4" t="n">
-        <v>3663000035.28595</v>
+        <v>3237500000</v>
       </c>
       <c r="G4" t="n">
-        <v>4047586035.28595</v>
+        <v>3815787000</v>
       </c>
       <c r="H4" t="n">
-        <v>2403367000</v>
+        <v>2977476095</v>
       </c>
       <c r="I4" t="n">
-        <v>196329000</v>
+        <v>168779762</v>
       </c>
       <c r="J4" t="n">
-        <v>269653000</v>
+        <v>247398615</v>
       </c>
       <c r="K4" t="n">
-        <v>-669365000</v>
+        <v>-620779373</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>15.01035046999644</v>
+        <v>15.42363929563632</v>
       </c>
       <c r="N4" t="n">
-        <v>1.684131485239645</v>
+        <v>1.281550843147911</v>
       </c>
       <c r="O4" t="n">
-        <v>1.200980861777022</v>
+        <v>1.005443213343714</v>
       </c>
       <c r="P4" t="n">
-        <v>5.359787008155836</v>
+        <v>5.213274501930502</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -758,72 +746,72 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>5449234777.120008</v>
+        <v>9081784280.301626</v>
       </c>
       <c r="T4" t="n">
-        <v>6731040247.148125</v>
+        <v>14902553184.37178</v>
       </c>
       <c r="U4" t="n">
-        <v>6335110595.159286</v>
+        <v>13431792299.27149</v>
       </c>
       <c r="V4" t="n">
-        <v>6171795206.475806</v>
+        <v>12472043254.6483</v>
       </c>
       <c r="W4" t="n">
-        <v>6.672211034027899</v>
+        <v>13.48329000502519</v>
       </c>
       <c r="X4" t="n">
-        <v>-40.6493586915762</v>
+        <v>-74.04194377859143</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>HRKET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6665271521</v>
+        <v>7584806686</v>
       </c>
       <c r="C5" t="n">
         <v>115200000</v>
       </c>
       <c r="D5" t="n">
-        <v>5749592318</v>
+        <v>5947660611</v>
       </c>
       <c r="E5" t="n">
-        <v>71.80000305175781</v>
+        <v>75.09999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>8271360351.5625</v>
+        <v>8651519824.21875</v>
       </c>
       <c r="G5" t="n">
-        <v>14020952669.5625</v>
+        <v>14599180435.21875</v>
       </c>
       <c r="H5" t="n">
-        <v>5948036961</v>
+        <v>7088413081</v>
       </c>
       <c r="I5" t="n">
-        <v>299269079</v>
+        <v>287087229</v>
       </c>
       <c r="J5" t="n">
-        <v>1378066171</v>
+        <v>1545454113</v>
       </c>
       <c r="K5" t="n">
-        <v>-1585711067</v>
+        <v>-1543371657</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>10.17436823036453</v>
+        <v>9.44653116026794</v>
       </c>
       <c r="N5" t="n">
-        <v>2.357240340215583</v>
+        <v>2.059583755685859</v>
       </c>
       <c r="O5" t="n">
-        <v>1.240963751514437</v>
+        <v>1.140638144435201</v>
       </c>
       <c r="P5" t="n">
-        <v>3.618136150282301</v>
+        <v>3.318344462395364</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -832,72 +820,72 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>24064246432.63884</v>
+        <v>54397046217.75619</v>
       </c>
       <c r="T5" t="n">
-        <v>11860705201.56267</v>
+        <v>30907241516.35742</v>
       </c>
       <c r="U5" t="n">
-        <v>13844306663.00128</v>
+        <v>31639255371.54433</v>
       </c>
       <c r="V5" t="n">
-        <v>16589752765.73426</v>
+        <v>38981181035.21931</v>
       </c>
       <c r="W5" t="n">
-        <v>144.0082705358877</v>
+        <v>338.3783075973899</v>
       </c>
       <c r="X5" t="n">
-        <v>-50.1417503421341</v>
+        <v>-77.80590635157478</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OZATD</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HKTM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4340799907</v>
+        <v>1053946708</v>
       </c>
       <c r="C6" t="n">
-        <v>71350000</v>
+        <v>105000000</v>
       </c>
       <c r="D6" t="n">
-        <v>1290640167</v>
+        <v>368577754</v>
       </c>
       <c r="E6" t="n">
-        <v>280.75</v>
+        <v>14.47999954223633</v>
       </c>
       <c r="F6" t="n">
-        <v>20031512500</v>
+        <v>1520399951.934814</v>
       </c>
       <c r="G6" t="n">
-        <v>21322152667</v>
+        <v>1888977705.934814</v>
       </c>
       <c r="H6" t="n">
-        <v>2457169440</v>
+        <v>912679851</v>
       </c>
       <c r="I6" t="n">
-        <v>154792470</v>
+        <v>38759791</v>
       </c>
       <c r="J6" t="n">
-        <v>448652223</v>
+        <v>90504327</v>
       </c>
       <c r="K6" t="n">
-        <v>-127228338</v>
+        <v>-148902048</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>47.52490141344959</v>
+        <v>20.87168391335383</v>
       </c>
       <c r="N6" t="n">
-        <v>8.677526392726095</v>
+        <v>2.0697046219056</v>
       </c>
       <c r="O6" t="n">
-        <v>4.614705337534002</v>
+        <v>1.442577637364578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.772744793983979</v>
+        <v>2.549315458125046</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -906,72 +894,72 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8415747895.578495</v>
+        <v>3165307227.513445</v>
       </c>
       <c r="T6" t="n">
-        <v>5984278462.137481</v>
+        <v>4376733530.464652</v>
       </c>
       <c r="U6" t="n">
-        <v>9016191596.380646</v>
+        <v>4396432291.934416</v>
       </c>
       <c r="V6" t="n">
-        <v>7805405984.698874</v>
+        <v>3979491016.637505</v>
       </c>
       <c r="W6" t="n">
-        <v>109.3960194071321</v>
+        <v>37.89991444416671</v>
       </c>
       <c r="X6" t="n">
-        <v>156.6363945612599</v>
+        <v>-61.79411021212744</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>HKTM</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OZATD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>986821330</v>
+        <v>4340799907</v>
       </c>
       <c r="C7" t="n">
-        <v>105000000</v>
+        <v>71350000</v>
       </c>
       <c r="D7" t="n">
-        <v>357765406</v>
+        <v>1290640167</v>
       </c>
       <c r="E7" t="n">
-        <v>14.47999954223633</v>
+        <v>966</v>
       </c>
       <c r="F7" t="n">
-        <v>1520399951.934814</v>
+        <v>68924100000</v>
       </c>
       <c r="G7" t="n">
-        <v>1878165357.934814</v>
+        <v>70214740167</v>
       </c>
       <c r="H7" t="n">
-        <v>793619301</v>
+        <v>2457169440</v>
       </c>
       <c r="I7" t="n">
-        <v>11388736</v>
+        <v>154792470</v>
       </c>
       <c r="J7" t="n">
-        <v>71595272</v>
+        <v>448652223</v>
       </c>
       <c r="K7" t="n">
-        <v>-117934052</v>
+        <v>-127228338</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>26.23309201108719</v>
+        <v>156.501487271133</v>
       </c>
       <c r="N7" t="n">
-        <v>2.366582258733164</v>
+        <v>28.5754572004607</v>
       </c>
       <c r="O7" t="n">
-        <v>1.540704386613547</v>
+        <v>15.87820251489883</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7490618495157833</v>
+        <v>0.2245839553944121</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -980,67 +968,67 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1191165944.057883</v>
+        <v>16227697412.39906</v>
       </c>
       <c r="T7" t="n">
-        <v>1991895851.909819</v>
+        <v>11484961111.69383</v>
       </c>
       <c r="U7" t="n">
-        <v>2049707513.199864</v>
+        <v>18107208589.48848</v>
       </c>
       <c r="V7" t="n">
-        <v>1744256436.389189</v>
+        <v>15273289037.86046</v>
       </c>
       <c r="W7" t="n">
-        <v>16.61196606084942</v>
+        <v>214.0615141956616</v>
       </c>
       <c r="X7" t="n">
-        <v>-12.83392050527747</v>
+        <v>351.2721511990397</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>EKOS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3138413474</v>
+        <v>3318993196</v>
       </c>
       <c r="C8" t="n">
         <v>1120000000</v>
       </c>
       <c r="D8" t="n">
-        <v>115978452</v>
+        <v>325644189</v>
       </c>
       <c r="E8" t="n">
-        <v>5.869999885559082</v>
+        <v>7.690000057220459</v>
       </c>
       <c r="F8" t="n">
-        <v>6574399871.826172</v>
+        <v>8612800064.086914</v>
       </c>
       <c r="G8" t="n">
-        <v>6690378323.826172</v>
+        <v>8938444253.086914</v>
       </c>
       <c r="H8" t="n">
-        <v>2322993973</v>
+        <v>2720238633</v>
       </c>
       <c r="I8" t="n">
-        <v>-189468737</v>
+        <v>-213663794</v>
       </c>
       <c r="J8" t="n">
-        <v>-73223798</v>
+        <v>-81055645</v>
       </c>
       <c r="K8" t="n">
-        <v>-462516187</v>
+        <v>-483340331</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>2.880067017645324</v>
+        <v>3.285904458767722</v>
       </c>
       <c r="O8" t="n">
-        <v>2.094816354279446</v>
+        <v>2.595003832628199</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
@@ -1050,69 +1038,69 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-1700142226.005995</v>
+        <v>-3490590396.846895</v>
       </c>
       <c r="T8" t="n">
-        <v>6761688124.201513</v>
+        <v>13817737049.74239</v>
       </c>
       <c r="U8" t="n">
-        <v>6518737973.758114</v>
+        <v>13844845050.36759</v>
       </c>
       <c r="V8" t="n">
-        <v>3860094623.984544</v>
+        <v>8057330567.75436</v>
       </c>
       <c r="W8" t="n">
-        <v>3.446513057129057</v>
+        <v>7.194045149780679</v>
       </c>
       <c r="X8" t="n">
-        <v>70.31706505266477</v>
+        <v>6.893964342924663</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SILVR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1600032227</v>
+        <v>1724268443</v>
       </c>
       <c r="C9" t="n">
         <v>350000000</v>
       </c>
       <c r="D9" t="n">
-        <v>132870054</v>
+        <v>122998426</v>
       </c>
       <c r="E9" t="n">
-        <v>2.559999942779541</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="F9" t="n">
-        <v>895999979.9728394</v>
+        <v>979999983.3106995</v>
       </c>
       <c r="G9" t="n">
-        <v>1028870033.972839</v>
+        <v>1102998409.310699</v>
       </c>
       <c r="H9" t="n">
-        <v>1827997665</v>
+        <v>1807540911</v>
       </c>
       <c r="I9" t="n">
-        <v>-169348630</v>
+        <v>-163779026</v>
       </c>
       <c r="J9" t="n">
-        <v>58000455</v>
+        <v>76096935</v>
       </c>
       <c r="K9" t="n">
-        <v>-246512468</v>
+        <v>-257055975</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>17.73899935738158</v>
+        <v>14.49464961119261</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5628399060197046</v>
+        <v>0.6102204396029294</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5599887082604614</v>
+        <v>0.5683569674369431</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
@@ -1122,70 +1110,70 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>1121943574.854172</v>
+        <v>2848327085.71509</v>
       </c>
       <c r="T9" t="n">
-        <v>5279265572.72679</v>
+        <v>9274978611.294996</v>
       </c>
       <c r="U9" t="n">
-        <v>3323396016.423572</v>
+        <v>7192611737.602843</v>
       </c>
       <c r="V9" t="n">
-        <v>3241535054.668178</v>
+        <v>6438639144.870976</v>
       </c>
       <c r="W9" t="n">
-        <v>9.261528727623366</v>
+        <v>18.39611184248851</v>
       </c>
       <c r="X9" t="n">
-        <v>-72.35877555349902</v>
+        <v>-84.77939264399733</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>SEKTÖR TOPLAM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21045353947</v>
+        <v>22681510669</v>
       </c>
       <c r="C10" t="n">
         <v>2816805333</v>
       </c>
       <c r="D10" t="n">
-        <v>8080566839</v>
+        <v>8785671453</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>43712897960.07584</v>
+        <v>94613631958.93826</v>
       </c>
       <c r="G10" t="n">
-        <v>51793464799.07584</v>
+        <v>103399303411.9383</v>
       </c>
       <c r="H10" t="n">
-        <v>17493710292</v>
+        <v>19887095951</v>
       </c>
       <c r="I10" t="n">
-        <v>501641472</v>
+        <v>521291898</v>
       </c>
       <c r="J10" t="n">
-        <v>2394016494</v>
+        <v>2648101004</v>
       </c>
       <c r="K10" t="n">
-        <v>-3074299132</v>
+        <v>-2877548100</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>21.63454801956592</v>
+        <v>39.04658593299573</v>
       </c>
       <c r="N10" t="n">
-        <v>2.960690667362964</v>
+        <v>5.199316364073707</v>
       </c>
       <c r="O10" t="n">
-        <v>2.077080673965432</v>
+        <v>4.171399045666373</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01147582282140531</v>
+        <v>0.005509691227435783</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1201,53 +1189,53 @@
       <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>SEKTÖR Median</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2325019613.5</v>
+        <v>2472120721.5</v>
       </c>
       <c r="C11" t="n">
         <v>113600000</v>
       </c>
       <c r="D11" t="n">
-        <v>245317730</v>
+        <v>347110971.5</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2892700060.367584</v>
+        <v>2590910034.179688</v>
       </c>
       <c r="G11" t="n">
-        <v>3114147792.367584</v>
+        <v>2952788960.179688</v>
       </c>
       <c r="H11" t="n">
-        <v>2075495819</v>
+        <v>2132355175.5</v>
       </c>
       <c r="I11" t="n">
-        <v>99339777</v>
+        <v>115396724</v>
       </c>
       <c r="J11" t="n">
-        <v>121975906.5</v>
+        <v>160525218</v>
       </c>
       <c r="K11" t="n">
-        <v>-186870403</v>
+        <v>-202979011.5</v>
       </c>
       <c r="L11" t="n">
-        <v>56.27869468672095</v>
+        <v>301.837293709779</v>
       </c>
       <c r="M11" t="n">
-        <v>15.01035046999644</v>
+        <v>14.49464961119261</v>
       </c>
       <c r="N11" t="n">
-        <v>2.087933166149209</v>
+        <v>2.06464418879573</v>
       </c>
       <c r="O11" t="n">
-        <v>1.715118375050295</v>
+        <v>1.507582509965681</v>
       </c>
       <c r="P11" t="n">
-        <v>4.488961579219068</v>
+        <v>4.265809482162933</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
